--- a/ig/main/CodeSystem-condition-ver-status.xlsx
+++ b/ig/main/CodeSystem-condition-ver-status.xlsx
@@ -108,7 +108,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/condition-ver-status|1.0.1</t>
+    <t>http://terminology.hl7.org/ValueSet/condition-ver-status</t>
   </si>
   <si>
     <t>Hierarchy</t>
